--- a/data_files/medicallist.xlsx
+++ b/data_files/medicallist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python_Selenium_Project\Python-Automation-Project\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA5B827A-90BF-4F4B-947E-6B4B257025FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1020F585-CE14-43CF-9E12-5406F9E795D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8EA63AA9-C735-4E9E-9A18-4FE660F2D614}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>medicinename</t>
   </si>
@@ -93,123 +93,6 @@
   </si>
   <si>
     <t>Antibiotic</t>
-  </si>
-  <si>
-    <t>Cetirizine</t>
-  </si>
-  <si>
-    <t>Cetirizine HCL</t>
-  </si>
-  <si>
-    <t>VAT003</t>
-  </si>
-  <si>
-    <t>R103</t>
-  </si>
-  <si>
-    <t>Allergy medicine</t>
-  </si>
-  <si>
-    <t>Ibuprofen</t>
-  </si>
-  <si>
-    <t>Ibuprofen 400mg</t>
-  </si>
-  <si>
-    <t>VAT004</t>
-  </si>
-  <si>
-    <t>R104</t>
-  </si>
-  <si>
-    <t>Pain killer</t>
-  </si>
-  <si>
-    <t>Azithromycin</t>
-  </si>
-  <si>
-    <t>Azithromycin 500mg</t>
-  </si>
-  <si>
-    <t>VAT005</t>
-  </si>
-  <si>
-    <t>R105</t>
-  </si>
-  <si>
-    <t>Omeprazole</t>
-  </si>
-  <si>
-    <t>Omeprazole 20mg</t>
-  </si>
-  <si>
-    <t>VAT006</t>
-  </si>
-  <si>
-    <t>R106</t>
-  </si>
-  <si>
-    <t>Gastric medicine</t>
-  </si>
-  <si>
-    <t>Dolo650</t>
-  </si>
-  <si>
-    <t>Paracetamol 650mg</t>
-  </si>
-  <si>
-    <t>VAT007</t>
-  </si>
-  <si>
-    <t>R107</t>
-  </si>
-  <si>
-    <t>Fever tablet</t>
-  </si>
-  <si>
-    <t>Crocin</t>
-  </si>
-  <si>
-    <t>Acetaminophen 650mg</t>
-  </si>
-  <si>
-    <t>VAT008</t>
-  </si>
-  <si>
-    <t>R108</t>
-  </si>
-  <si>
-    <t>Common medicine</t>
-  </si>
-  <si>
-    <t>VitaminC</t>
-  </si>
-  <si>
-    <t>Ascorbic Acid</t>
-  </si>
-  <si>
-    <t>VAT009</t>
-  </si>
-  <si>
-    <t>R109</t>
-  </si>
-  <si>
-    <t>Supplement</t>
-  </si>
-  <si>
-    <t>ORS</t>
-  </si>
-  <si>
-    <t>Oral Rehydration Salt</t>
-  </si>
-  <si>
-    <t>VAT010</t>
-  </si>
-  <si>
-    <t>R110</t>
-  </si>
-  <si>
-    <t>Hydration</t>
   </si>
 </sst>
 </file>
@@ -685,237 +568,93 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2">
-        <v>40</v>
-      </c>
-      <c r="E4" s="2">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2">
-        <v>15</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="2">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2">
-        <v>35</v>
-      </c>
-      <c r="E6" s="2">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="2">
-        <v>6</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="2">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2">
-        <v>50</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2">
-        <v>30</v>
-      </c>
-      <c r="D8" s="2">
-        <v>60</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="2">
-        <v>15</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="2">
-        <v>12</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="2">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2">
-        <v>80</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="2">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="2">
-        <v>50</v>
-      </c>
-      <c r="D11" s="2">
-        <v>100</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="2">
-        <v>25</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>57</v>
-      </c>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
